--- a/valora-demo/modelos/inretail-modelo.xlsx
+++ b/valora-demo/modelos/inretail-modelo.xlsx
@@ -6008,11 +6008,11 @@
         </is>
       </c>
       <c r="C28" s="29" t="n">
-        <v>0.1048008837827988</v>
+        <v>0.0583</v>
       </c>
       <c r="D28" s="27" t="inlineStr">
         <is>
-          <t>Default: |gastos financieros| / deuda financiera promedio (histórico)</t>
+          <t>Kd real ponderado por instrumento en PEN (deuda_financiera SMV, 100% saldo, 13/16 instrumentos) — ver kd_real.py</t>
         </is>
       </c>
     </row>
